--- a/data_voor_swing/aggregatietabellen/treg_gem_treg.xlsx
+++ b/data_voor_swing/aggregatietabellen/treg_gem_treg.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\gebiedsniveaus\data_voor_swing\aggregatietabellen\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{058D708D-281F-47B5-8050-4ACF9FB7C164}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="52">
   <si>
     <t>TREG_gem</t>
   </si>
@@ -119,6 +113,9 @@
   </si>
   <si>
     <t>TREG06A</t>
+  </si>
+  <si>
+    <t>TREG06B</t>
   </si>
   <si>
     <t>TREG07</t>
@@ -178,8 +175,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -238,25 +235,17 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standaard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -294,7 +283,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -328,7 +317,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -363,10 +351,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -539,14 +526,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -554,7 +538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -562,7 +546,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -570,7 +554,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -578,7 +562,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -586,7 +570,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -594,7 +578,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>7</v>
       </c>
@@ -602,163 +586,169 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
       <c r="A20" t="s">
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
       <c r="A21" t="s">
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
       <c r="A22" t="s">
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
       <c r="A23" t="s">
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
       <c r="A24" t="s">
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
       <c r="A25" t="s">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
       <c r="A26" t="s">
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
       <c r="A27" t="s">
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
       <c r="A28" t="s">
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>
